--- a/Work/Data_Info/Meta_kre.xlsx
+++ b/Work/Data_Info/Meta_kre.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,11 @@
           <t>var</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -422,6 +427,11 @@
           <t>Population</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -459,6 +469,11 @@
           <t>New.Housing.per.Capita</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -496,6 +511,11 @@
           <t>Permit.Housing.perCapita</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -533,6 +553,11 @@
           <t>Age.below.6</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -570,6 +595,11 @@
           <t>Age.6.18</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -607,6 +637,11 @@
           <t>Age.65</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,6 +679,11 @@
           <t>School.Primary</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -681,6 +721,11 @@
           <t>School.SpecialEdu</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -718,6 +763,11 @@
           <t>Migration.Balance</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -755,6 +805,11 @@
           <t>Purchasing.Power</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -792,6 +847,11 @@
           <t>Recreation.Area.per.Capita</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -829,6 +889,11 @@
           <t>Forest.Area</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,95 +931,110 @@
           <t>Water.Area</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zuweisungen für Investitionsfördermaßnahmen in € je Einwohner</t>
+          <t>Einwohner je km²</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zuweisungen für Investitionsfördermaßnahmen</t>
+          <t>Einwohnerdichte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zuweisungen für Investitionsfördermaßnahmen  &lt;Zeitpunkt&gt; / E &lt;Zeiitpunkt&gt;</t>
+          <t>E &lt;Zeitpunkt&gt; / Fläche &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Vierteljährliche Kassenstatistik des Bundes und der Länder</t>
+          <t>Laufende Raumbeobachtung des BBSR; Fortschreibung des Bevölkerungsstandes des Bundes und der Länder</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Als Investitionszuweisungen bezeichnet man Finanztransfers von einer Einheit des öffentlichen Sektors an eine andere Einheit des öffentlichen Sektors (z.B. vom Land an eine Kommune). Die Finanztransfers dienen dabei der Investitionsfinanzierung. Investitionszuweisungen sind in der Bilanz des Zuweisungsempfängers bei den Sonderposten zu erfassen. Bei den Bevölkerungszahlen handelt es sich um die Fortschreibung des Bevölkerungsstandes des Bundes und der Länder zum Stichtag 31.12. des Jahres. Die Fortschreibung basiert auf der Volkszählung 1987 (BRD) bzw. 1981 (DDR), dem Zensus 2011 sowie dem Zensus 2022.</t>
+          <t>Die Einwohnerdichte ist ein generelles Maß der regionalen Bevölkerungsverteilung und das am häufigsten verwendete Dichtemaß. Sie gibt Aufschluss zur Beurteilung des Arbeitsmarktes, der Auslastung von Infrastruktur, der Belastung der Umwelt usw. Zudem findet die Einwohnerdichte oft als zentraler Indikator Eingang in die Typisierung bzw. Differenzierung eher städtischer oder eher ländlicher Gebiete. Bei den Bevölkerungszahlen handelt es sich um die Fortschreibung des Bevölkerungsstandes des Bundes und der Länder zum Stichtag 31.12. des Jahres. Die Fortschreibung basiert auf der Volkszählung 1987 (BRD) bzw. 1981 (DDR), dem Zensus 2011 sowie dem Zensus 2022.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Investment.Allocations</t>
+          <t>Population.Density</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Einwohner je km²</t>
+          <t>Durchschn. Pkw-Fahrzeit zur nächsten BAB-Anschlussstelle in Minuten</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Einwohnerdichte</t>
+          <t>Erreichbarkeit von Autobahnen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E &lt;Zeitpunkt&gt; / Fläche &lt;Zeitpunkt&gt;</t>
+          <t>Pkw-Fahrzeit zur nächsten BAB-Anschlussstelle in Minuten &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Fortschreibung des Bevölkerungsstandes des Bundes und der Länder</t>
+          <t>Laufende Raumbeobachtung des BBSR; Erreichbarkeitsmodell des BBSR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Die Einwohnerdichte ist ein generelles Maß der regionalen Bevölkerungsverteilung und das am häufigsten verwendete Dichtemaß. Sie gibt Aufschluss zur Beurteilung des Arbeitsmarktes, der Auslastung von Infrastruktur, der Belastung der Umwelt usw. Zudem findet die Einwohnerdichte oft als zentraler Indikator Eingang in die Typisierung bzw. Differenzierung eher städtischer oder eher ländlicher Gebiete. Bei den Bevölkerungszahlen handelt es sich um die Fortschreibung des Bevölkerungsstandes des Bundes und der Länder zum Stichtag 31.12. des Jahres. Die Fortschreibung basiert auf der Volkszählung 1987 (BRD) bzw. 1981 (DDR), dem Zensus 2011 sowie dem Zensus 2022.</t>
+          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzellenebene ermittelten Pkw-Fahrtzeiten zur zeitnächsten Bundesautobahnanschlussstelle. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Population.Density</t>
+          <t>Highway.Access</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Durchschn. Pkw-Fahrzeit zur nächsten BAB-Anschlussstelle in Minuten</t>
+          <t>Durchschn. Pkw-Fahrzeit zum nächsten internationalen Flughafen in Deutschland in Minuten</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Erreichbarkeit von Autobahnen</t>
+          <t>Erreichbarkeit von Flughäfen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pkw-Fahrzeit zur nächsten BAB-Anschlussstelle in Minuten &lt;Zeitpunkt&gt;</t>
+          <t>Pkw-Fahrzeit zum nächsten internationalen Flughafen in Minuten &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -964,34 +1044,39 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzellenebene ermittelten Pkw-Fahrtzeiten zur zeitnächsten Bundesautobahnanschlussstelle. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
+          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzellenebene ermittelten Pkw-Fahrtzeiten zum zeitnächsten Hauptverkehrsflughafen in Deutschland oder dem benachbartem Ausland. Grundlage für die Auswahl der Flughäfen bildet die Luftverkehrsstatistik des Statistischen Bundesamtes sowie Daten des World Airport Traffic Report. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Highway.Access</t>
+          <t>Airport.Access</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Durchschn. Pkw-Fahrzeit zum nächsten internationalen Flughafen in Deutschland in Minuten</t>
+          <t>Durchschn. Pkw-Fahrzeit zum nächsten IC/ICE-Bahnhof in Minuten</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Erreichbarkeit von Flughäfen</t>
+          <t>Erreichbarkeit von IC/EC/ICE-Bahnhöfen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pkw-Fahrzeit zum nächsten internationalen Flughafen in Minuten &lt;Zeitpunkt&gt;</t>
+          <t>Pkw-Fahrzeit zum nächsten Bahnhof (Fernverkehr) in Minuten &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1001,108 +1086,123 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzellenebene ermittelten Pkw-Fahrtzeiten zum zeitnächsten Hauptverkehrsflughafen in Deutschland oder dem benachbartem Ausland. Grundlage für die Auswahl der Flughäfen bildet die Luftverkehrsstatistik des Statistischen Bundesamtes sowie Daten des World Airport Traffic Report. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
+          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzelleneben ermittelten Pkw-Fahrtzeiten zum zeitnächsten IC-, EC- oder ICE-Haltepunkt. Bei den ausgewählten Bahnhöfen handelt es sich um alle IC-, EC- und ICE-Systemhalte der DB AG, selbst diejenigen in denen eine Bedienung nur durch einzelne Züge erfolgt. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Airport.Access</t>
+          <t>Highspeed.Rail.Access</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Durchschn. Pkw-Fahrzeit zum nächsten IC/ICE-Bahnhof in Minuten</t>
+          <t>Einwohnergewichtete Entfernung zum nächsten Supermarkt oder Discounter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Erreichbarkeit von IC/EC/ICE-Bahnhöfen</t>
+          <t>Entfernung zum Supermarkt/Discounter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pkw-Fahrzeit zum nächsten Bahnhof (Fernverkehr) in Minuten &lt;Zeitpunkt&gt;</t>
+          <t>Summe (Entfernung vom Messgittermittelpunkt zum nächsten Supermarkt/Discounter * Einwohnerzahl am Messpunktgitter) &lt;Zeitpunkt&gt; / Einwohner &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Erreichbarkeitsmodell des BBSR</t>
+          <t>Laufende Raumbeobachtung des BBSR; POI Bund: BKG/GeoBasis-DE, infas360 GmbH; OSM Mitwirkende; Zensus 2022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Es handelt sich um den bevölkerungsgewichteten Durchschnittswert der auf der 100 m-Gitterzelleneben ermittelten Pkw-Fahrtzeiten zum zeitnächsten IC-, EC- oder ICE-Haltepunkt. Bei den ausgewählten Bahnhöfen handelt es sich um alle IC-, EC- und ICE-Systemhalte der DB AG, selbst diejenigen in denen eine Bedienung nur durch einzelne Züge erfolgt. Die Erreichbarkeitsberechnungen des motorisierten Individualverkehrs basieren auf Routensuchen in einem Straßennetzmodell. Die Ermittlung der für Straßentypen zugrunde gelegten Pkw-Geschwindigkeiten erfolgt in Abhängigkeit von Ausbaustand sowie siedlungsstrukturellen und topographischen Gegebenheiten.</t>
+          <t>Indikator zur fußläufigen Erreichbarkeit des nächsten Supermarktes oder Discounter. Enthält die durchschnittliche, einwohnergewichtete Entfernung zum nächsten Supermarkt oder Discounter. Datengrundlage der Zielpunkte sind Standortdaten aus dem POI Bund Datensatz (Quelle: infas360 GmbH) sowie Ergänzungen aus OpenStreetMap (u.a. Nahversorger, Dorfläden, inhabergeführte Lebensmittelläden). Datengrundlage der Startpunkte sind Einwohnerzahlen des Zensus im 100x100m-Raster. Die Ermittlung der Distanzen erfolgt im 100x100m-Raster mit dem PathDistance-Algorithmus entlang von für Fußgänger passierbaren Wegesegmenten aus OpenStreetMap. Aufgrund wechselnder Datengrundlagen und Methoden der Distanzermittlung nicht für Zeitvergleiche geeignet.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Highspeed.Rail.Access</t>
+          <t>Supermarket.Access</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Einwohnergewichtete Entfernung zum nächsten Supermarkt oder Discounter</t>
+          <t>Anteil Einwohner mit max. 1000m Entfernung zur nächsten Hausarztpraxis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entfernung zum Supermarkt/Discounter</t>
+          <t>Nahversorgung Hausarzt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Summe (Entfernung vom Messgittermittelpunkt zum nächsten Supermarkt/Discounter * Einwohnerzahl am Messpunktgitter) &lt;Zeitpunkt&gt; / Einwohner &lt;Zeitpunkt&gt;</t>
+          <t>Einwohner mit max. 1km Entfernung zur nächsten Hausarztpraxis &lt;Zeitpunkt&gt; / Einwohner &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; POI Bund: BKG/GeoBasis-DE, infas360 GmbH; OSM Mitwirkende; Zensus 2022</t>
+          <t>Laufende Raumbeobachtung des BBSR; POI Bund: BKG/GeoBasis-DE, infas360 GmbH; Zensus 2022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Indikator zur fußläufigen Erreichbarkeit des nächsten Supermarktes oder Discounter. Enthält die durchschnittliche, einwohnergewichtete Entfernung zum nächsten Supermarkt oder Discounter. Datengrundlage der Zielpunkte sind Standortdaten aus dem POI Bund Datensatz (Quelle: infas360 GmbH) sowie Ergänzungen aus OpenStreetMap (u.a. Nahversorger, Dorfläden, inhabergeführte Lebensmittelläden). Datengrundlage der Startpunkte sind Einwohnerzahlen des Zensus im 100x100m-Raster. Die Ermittlung der Distanzen erfolgt im 100x100m-Raster mit dem PathDistance-Algorithmus entlang von für Fußgänger passierbaren Wegesegmenten aus OpenStreetMap. Aufgrund wechselnder Datengrundlagen und Methoden der Distanzermittlung nicht für Zeitvergleiche geeignet.</t>
+          <t>Indikator zur fußläufigen Erreichbarkeit der nächsten Hausarztpraxis. Enthält den Anteil der Einwohner mit einer Entfernung von max. 1000m zur nächsten Hausarztpraxis. Datengrundlage der Zielpunkte sind Standortdaten aus dem POI Bund Datensatz (Quelle: infas360 GmbH). Als Hausärzte sind definiert: Fachärzte für Allgemeinmedizin, Fachärzte für Innere und Allgemeinmedizin, Internisten, Praktische Ärzte ohne Schwerpunktbezeichnung. Datengrundlage der Startpunkte sind Einwohnerzahlen des Zensus im 100x100m-Raster. Die Ermittlung der Distanzen erfolgt im 100x100m-Raster mit dem PathDistance-Algorithmus entlang von für Fußgänger passierbaren Wegesegmenten aus OpenStreetMap. Aufgrund wechselnder Datengrundlagen und Methoden der Distanzermittlung nicht für Zeitvergleiche geeignet.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Supermarket.Access</t>
+          <t>Doc.GP</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Anteil Einwohner mit max. 1000m Entfernung zur nächsten Hausarztpraxis</t>
+          <t>Einwohnergewichtete Entfernung zur nächsten Apotheke</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nahversorgung Hausarzt</t>
+          <t>Entfernung zur Apotheke</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Einwohner mit max. 1km Entfernung zur nächsten Hausarztpraxis &lt;Zeitpunkt&gt; / Einwohner &lt;Zeitpunkt&gt; x 100</t>
+          <t>Summe (Entfernung vom Messgittermittelpunkt zur nächsten Apotheke * Einwohnerzahl am Messpunktgitter) &lt;Zeitpunkt&gt; / Einwohner &lt;Zeitpunkt&gt;</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1112,17 +1212,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Indikator zur fußläufigen Erreichbarkeit der nächsten Hausarztpraxis. Enthält den Anteil der Einwohner mit einer Entfernung von max. 1000m zur nächsten Hausarztpraxis. Datengrundlage der Zielpunkte sind Standortdaten aus dem POI Bund Datensatz (Quelle: infas360 GmbH). Als Hausärzte sind definiert: Fachärzte für Allgemeinmedizin, Fachärzte für Innere und Allgemeinmedizin, Internisten, Praktische Ärzte ohne Schwerpunktbezeichnung. Datengrundlage der Startpunkte sind Einwohnerzahlen des Zensus im 100x100m-Raster. Die Ermittlung der Distanzen erfolgt im 100x100m-Raster mit dem PathDistance-Algorithmus entlang von für Fußgänger passierbaren Wegesegmenten aus OpenStreetMap. Aufgrund wechselnder Datengrundlagen und Methoden der Distanzermittlung nicht für Zeitvergleiche geeignet.</t>
+          <t>Indikator zur fußläufigen Erreichbarkeit der nächsten Apotheke. Enthält die durchschnittliche, einwohnergewichtete Entfernung zur nächsten Apotheke. Datengrundlage der Zielpunkte sind Standortdaten aus dem POI Bund Datensatz (Quelle: infas360 GmbH). Datengrundlage der Startpunkte sind Einwohnerzahlen des Zensus im 100x100m-Raster. Die Ermittlung der Distanzen erfolgt im 100x100m-Raster mit dem PathDistance-Algorithmus entlang von für Fußgänger passierbaren Wegesegmenten aus OpenStreetMap. Aufgrund wechselnder Datengrundlagen und Methoden der Distanzermittlung nicht für Zeitvergleiche geeignet.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Pharmacy.Access</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
@@ -1165,6 +1270,11 @@
           <t>Broadband.50Mbps</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1205,6 +1315,11 @@
           <t>Broadband.100Mbps</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1245,6 +1360,11 @@
           <t>Broadband.1000Mbps</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1282,6 +1402,11 @@
           <t>Public.Transport.Access</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1319,6 +1444,11 @@
           <t>Traffic.Accidents</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1356,6 +1486,11 @@
           <t>Child.Poverty</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1393,6 +1528,11 @@
           <t>Daycare</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1430,6 +1570,11 @@
           <t>Emp.Rate</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1467,6 +1612,11 @@
           <t>Emp.Rate.Women</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1504,95 +1654,110 @@
           <t>Unemp.Men</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Durchschnittliche Kaufwerte für Bauland in € je m²</t>
+          <t>Zuweisungen für Investitionsfördermaßnahmen in € je Einwohner</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Baulandpreise</t>
+          <t>Zuweisungen für Investitionsfördermaßnahmen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kaufsumme für baureifes Land &lt;Durchschnitt zwei Jahre&gt; / Umgesetzte Fläche für baureifes Land &lt;Durchschnitt zwei Jahre&gt;</t>
+          <t>Zuweisungen für Investitionsfördermaßnahmen  &lt;Zeitpunkt&gt; / E &lt;Zeiitpunkt&gt;</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik der Kaufwerte für Bauland des Bundes und der Länder</t>
+          <t>Laufende Raumbeobachtung des BBSR; Vierteljährliche Kassenstatistik des Bundes und der Länder</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grundstückspreise können je nach Marktlage einen hohen Anteil an den Bau- und Immobilienkosten ausmachen. Die Kaufsumme ist die Gesamtsumme aus den Kaufpreisen der veräußerten Grundstücke. Der Kaufpreis für das Grundstück versteht sich ohne Grunderwerbsnebenkosten (Vermessungskosten, Makler-, Notariats- und Gerichtsgebühren, Grunderwerbsteuer u.a.). Er beinhaltet jedoch evtl. besonders vereinbarte Beträge für Aufwuchs, Zäune, den Kapitalwert von Leibrenten sowie die Erschließungskosten. Die veräußerte Fläche umschließt alle durch Kauf erworbenen, unbebauten Grundstücke innerhalb des Baugebiets einer Gemeinde einer Mindestgröße von 100 m². Der Zwei-Jahresdurchschnitt federt kurzfristige Schwankungen auf dem Markt und in der Statistik ab, die durch Veröffentlichungsrestriktionen und Art der Veräußerungsfälle entstehen können.</t>
+          <t>Als Investitionszuweisungen bezeichnet man Finanztransfers von einer Einheit des öffentlichen Sektors an eine andere Einheit des öffentlichen Sektors (z.B. vom Land an eine Kommune). Die Finanztransfers dienen dabei der Investitionsfinanzierung. Investitionszuweisungen sind in der Bilanz des Zuweisungsempfängers bei den Sonderposten zu erfassen. Bei den Bevölkerungszahlen handelt es sich um die Fortschreibung des Bevölkerungsstandes des Bundes und der Länder zum Stichtag 31.12. des Jahres. Die Fortschreibung basiert auf der Volkszählung 1987 (BRD) bzw. 1981 (DDR), dem Zensus 2011 sowie dem Zensus 2022.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Land.Price</t>
+          <t>Investment.Allocations</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort im Primären Sektor an den SV Beschäftigten in %</t>
+          <t>Durchschnittliche Kaufwerte für Bauland in € je m²</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Beschäftigte Pimärer Sektor</t>
+          <t>Baulandpreise</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO im Primären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>Kaufsumme für baureifes Land &lt;Durchschnitt zwei Jahre&gt; / Umgesetzte Fläche für baureifes Land &lt;Durchschnitt zwei Jahre&gt;</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Beschäftigtenstatistik der Bundesagentur für Arbeit</t>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik der Kaufwerte für Bauland des Bundes und der Länder</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Der Anteil der im primären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der primäre Sektor umfasst den Wirtschaftsabschnitt (WZ 2008) A (Land- und Forstwirtschaft, Fischerei). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
+          <t>Grundstückspreise können je nach Marktlage einen hohen Anteil an den Bau- und Immobilienkosten ausmachen. Die Kaufsumme ist die Gesamtsumme aus den Kaufpreisen der veräußerten Grundstücke. Der Kaufpreis für das Grundstück versteht sich ohne Grunderwerbsnebenkosten (Vermessungskosten, Makler-, Notariats- und Gerichtsgebühren, Grunderwerbsteuer u.a.). Er beinhaltet jedoch evtl. besonders vereinbarte Beträge für Aufwuchs, Zäune, den Kapitalwert von Leibrenten sowie die Erschließungskosten. Die veräußerte Fläche umschließt alle durch Kauf erworbenen, unbebauten Grundstücke innerhalb des Baugebiets einer Gemeinde einer Mindestgröße von 100 m². Der Zwei-Jahresdurchschnitt federt kurzfristige Schwankungen auf dem Markt und in der Statistik ab, die durch Veröffentlichungsrestriktionen und Art der Veräußerungsfälle entstehen können.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Emp.Primary</t>
+          <t>Land.Price</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort im Sekundären Sektor an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort im Primären Sektor an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Beschäftigte Sekundärer Sektor</t>
+          <t>Beschäftigte Pimärer Sektor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO im Sekundären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO im Primären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1602,34 +1767,39 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Der Anteil der im sekundären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der sekundäre Sektor umfasst das Produzierende Gewerbe und damit die Wirtschaftsabschnitte (WZ 2008) B (Bergbau und Gewinnung von Steinen und Erden), C (Verarbeitendes Gewerbe), D (Energieversorgung), E (Wasserversorgung, Abwasser/Abfall, Umweltverschmutzung) und F (Baugewerbe). Der sekundäre Sektor bietet in der Regel gute Verdienstmöglichkeiten, aber z.T. strukturelle Gefährdungspotentiale bei „klassischen“ Produktionen. Es herrscht eine hohe Heterogenität von Produktivität und Modernität innerhalb des Sektors. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
+          <t>Der Anteil der im primären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der primäre Sektor umfasst den Wirtschaftsabschnitt (WZ 2008) A (Land- und Forstwirtschaft, Fischerei). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Emp.Secundary</t>
+          <t>Emp.Primary</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort im Tertiären Sektor an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort im Sekundären Sektor an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Beschäftigte Tertiärer Sektor</t>
+          <t>Beschäftigte Sekundärer Sektor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO im Tertiären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO im Sekundären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1639,34 +1809,39 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Der Anteil der im tertiären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der tertiäre Sektor umfasst den Dienstleistungssektor und damit die Wirtschaftsabschnitte (WZ 2008) G (Handel, Instandhaltung v. Kfz), H (Verkehr u. Lagerei), I (Gastgewerbe), J (Information und Kommunikation), K (Finanz- und Versicherungsdienstleistungen), L (Grundstücks- u. Wohnungswesen), M (freiberufliche, wissenschaftliche u. technische Dienstleistungen), N (Sonstige wirtschaftliche Dienstleistungen), O (Öffentliche Verwaltung, Verteidigung; Sozialversicherung), P (Erziehung u. Unterricht), Q (Gesundheits- u. Sozialwesen), R (Kunst, Unterhaltung, Erholung), S (Erbringung von sonstigen Dienstleistungen), T (Private Haushalte, Dienstleistungen f. priv. HH). Tertiärisierung wird z.T. als Indikator für den Reifegrad einer Wirtschaft interpretiert, was im Einzelfall aber zu Fehleinschätzungen führen kann. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
+          <t>Der Anteil der im sekundären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der sekundäre Sektor umfasst das Produzierende Gewerbe und damit die Wirtschaftsabschnitte (WZ 2008) B (Bergbau und Gewinnung von Steinen und Erden), C (Verarbeitendes Gewerbe), D (Energieversorgung), E (Wasserversorgung, Abwasser/Abfall, Umweltverschmutzung) und F (Baugewerbe). Der sekundäre Sektor bietet in der Regel gute Verdienstmöglichkeiten, aber z.T. strukturelle Gefährdungspotentiale bei „klassischen“ Produktionen. Es herrscht eine hohe Heterogenität von Produktivität und Modernität innerhalb des Sektors. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Emp.Tertiary</t>
+          <t>Emp.Secundary</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort in Kreativbranchen an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort im Tertiären Sektor an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Beschäftigte in Kreativbranchen</t>
+          <t>Beschäftigte Tertiärer Sektor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO in Kreativbranchen &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO im Tertiären Sektor &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1676,34 +1851,39 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Der Anteil der in Kreativbranchen tätigen sozialversicherungspflichtig Beschäftigten. Die Abgrenzung der Kultur- und Kreativwirtschaft erfolgt nach dem Arbeitskreis Kulturstatistik e.V. anhand der Klassifikation der Wirtschaftszweige (WZ 2008): Verlagsgewerbe, Filmwirtschaft, Tonträgerindustrie/Musikverlage, Rundfunkwirtschaft, kulturelle Wirtschaftszweige, Bibliotheken/Museen, Handel mit Kulturgütern, Architektur, Design, Werbung, Software/Games. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Besonders in der Kreativwirtschaft sind häufig Freiberufler und Selbstständige tätig, weswegen die SV Beschäftigten insbesondere für diese Gruppe nur eine eingeschränkte Aussagekraft aufweisen. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
+          <t>Der Anteil der im tertiären Sektor tätigen sozialversicherungspflichtig Beschäftigten. Der tertiäre Sektor umfasst den Dienstleistungssektor und damit die Wirtschaftsabschnitte (WZ 2008) G (Handel, Instandhaltung v. Kfz), H (Verkehr u. Lagerei), I (Gastgewerbe), J (Information und Kommunikation), K (Finanz- und Versicherungsdienstleistungen), L (Grundstücks- u. Wohnungswesen), M (freiberufliche, wissenschaftliche u. technische Dienstleistungen), N (Sonstige wirtschaftliche Dienstleistungen), O (Öffentliche Verwaltung, Verteidigung; Sozialversicherung), P (Erziehung u. Unterricht), Q (Gesundheits- u. Sozialwesen), R (Kunst, Unterhaltung, Erholung), S (Erbringung von sonstigen Dienstleistungen), T (Private Haushalte, Dienstleistungen f. priv. HH). Tertiärisierung wird z.T. als Indikator für den Reifegrad einer Wirtschaft interpretiert, was im Einzelfall aber zu Fehleinschätzungen führen kann. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emp.Creative</t>
+          <t>Emp.Tertiary</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit akademischem Berufsabschluss an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort in Kreativbranchen an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Beschäftigte am AO mit akademischem Berufsabschluss</t>
+          <t>Beschäftigte in Kreativbranchen</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO mit akademischem Berufsabschluss &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO in Kreativbranchen &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1713,34 +1893,39 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit einem akademischen Abschluss (dazu zählen Bachelor, Diplom, Magister, Master, Staatsexamen, Promotion) nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Der Anteil der in Kreativbranchen tätigen sozialversicherungspflichtig Beschäftigten. Die Abgrenzung der Kultur- und Kreativwirtschaft erfolgt nach dem Arbeitskreis Kulturstatistik e.V. anhand der Klassifikation der Wirtschaftszweige (WZ 2008): Verlagsgewerbe, Filmwirtschaft, Tonträgerindustrie/Musikverlage, Rundfunkwirtschaft, kulturelle Wirtschaftszweige, Bibliotheken/Museen, Handel mit Kulturgütern, Architektur, Design, Werbung, Software/Games. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Besonders in der Kreativwirtschaft sind häufig Freiberufler und Selbstständige tätig, weswegen die SV Beschäftigten insbesondere für diese Gruppe nur eine eingeschränkte Aussagekraft aufweisen. Es handelt sich um SV Beschäftigte am Arbeitsort.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Emp.AO.Academic</t>
+          <t>Emp.Creative</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Berufsabschluss an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit akademischem Berufsabschluss an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Beschäftigte am AO mit Berufsabschluss</t>
+          <t>Beschäftigte am AO mit akademischem Berufsabschluss</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO mit Berufsabschluss, ohne akadem. Abschluss &lt;Zeitpunkt&gt; / SV Beschäftigte  AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO mit akademischem Berufsabschluss &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1750,34 +1935,39 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit einem anerkannten Berufsabschluss (dazu zählen Abschlüsse einer anerkannten Berufsausbildung, Meister-/Techniker- oder gleichwertiger Fachschulabschluss, nicht aber akademische Abschlüsse) nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit einem akademischen Abschluss (dazu zählen Bachelor, Diplom, Magister, Master, Staatsexamen, Promotion) nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Emp.AO.Vocational</t>
+          <t>Emp.AO.Academic</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort ohne Berufsabschluss an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Berufsabschluss an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Beschäftigte am AO ohne Berufsabschluss</t>
+          <t>Beschäftigte am AO mit Berufsabschluss</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO ohne Berufsabschluss &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO mit Berufsabschluss, ohne akadem. Abschluss &lt;Zeitpunkt&gt; / SV Beschäftigte  AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1787,34 +1977,39 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort ohne einen beruflichen Ausbildungsabschluss nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit einem anerkannten Berufsabschluss (dazu zählen Abschlüsse einer anerkannten Berufsausbildung, Meister-/Techniker- oder gleichwertiger Fachschulabschluss, nicht aber akademische Abschlüsse) nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Emp.AO.NoTrain</t>
+          <t>Emp.AO.Vocational</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Experte an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort ohne Berufsabschluss an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Beschäftigte mit Anforderungsniveau Experte</t>
+          <t>Beschäftigte am AO ohne Berufsabschluss</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO Anforderungsniveau Experte &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO ohne Berufsabschluss &lt;Zeitpunkt&gt; / SV Beschäftigte AO &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1824,34 +2019,39 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Experte nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Experte zählen hoch komplexe Tätigkeiten mit einem sehr hohen Kenntnis- und Fertigkeitsniveau sowie Leitungs- und Führungsaufgaben und mindestens einer vierjährigen Hochschulausbildung bzw. einer entsprechenden Berufserfahrung. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort ohne einen beruflichen Ausbildungsabschluss nach Klassifikation der Berufe 2010 (KldB 2010). Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emp.Expert</t>
+          <t>Emp.AO.NoTrain</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Spezialist an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Experte an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Beschäftigte mit Anforderungsniveau Spezialist</t>
+          <t>Beschäftigte mit Anforderungsniveau Experte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO Anforderungsniveau Spezialist &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO Anforderungsniveau Experte &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1861,34 +2061,39 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Spezialist nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Spezialist zählen komplexe Spezialistentätigkeiten mit notwendigen Spezialkenntnissen und -Fertigkeiten sowie häufig gehobenen Fach- und Führungsaufgaben. Notwendig ist eine Meister- oder Technikerausbildung oder gleichwertiger Fachschul- oder Hochschulabschluss. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Experte nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Experte zählen hoch komplexe Tätigkeiten mit einem sehr hohen Kenntnis- und Fertigkeitsniveau sowie Leitungs- und Führungsaufgaben und mindestens einer vierjährigen Hochschulausbildung bzw. einer entsprechenden Berufserfahrung. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emp.Specialist</t>
+          <t>Emp.Expert</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Fachkraft an den SV Beschäftigten in %</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Spezialist an den SV Beschäftigten in %</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Beschäftigte mit Anforderungsniveau Fachkraft</t>
+          <t>Beschäftigte mit Anforderungsniveau Spezialist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SV Beschäftigte AO Anforderungsniveau Fachkraft &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
+          <t>SV Beschäftigte AO Anforderungsniveau Spezialist &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1898,146 +2103,166 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Fachkraft nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Fachkraft zählen fachlich ausgerichtete Tätigkeiten mit fundierten Fachkenntnissen und Fertigkeiten. Der Abschluss einer mindestens zweijährigen Berufsausbildung oder vergleichbare Qualifikation ist hierzu notwendig. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Spezialist nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Spezialist zählen komplexe Spezialistentätigkeiten mit notwendigen Spezialkenntnissen und -Fertigkeiten sowie häufig gehobenen Fach- und Führungsaufgaben. Notwendig ist eine Meister- oder Technikerausbildung oder gleichwertiger Fachschul- oder Hochschulabschluss. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Emp.Professional</t>
+          <t>Emp.Specialist</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Fachkraft an den SV Beschäftigten in %</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Beschäftigte mit Anforderungsniveau Fachkraft</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SV Beschäftigte AO Anforderungsniveau Fachkraft &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Laufende Raumbeobachtung des BBSR; Beschäftigtenstatistik der Bundesagentur für Arbeit</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Fachkraft nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Fachkraft zählen fachlich ausgerichtete Tätigkeiten mit fundierten Fachkenntnissen und Fertigkeiten. Der Abschluss einer mindestens zweijährigen Berufsausbildung oder vergleichbare Qualifikation ist hierzu notwendig. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Emp.Professional</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Helfer an den SV Beschäftigten in %</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Beschäftigte mit Anforderungsniveau Helfer</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>SV Beschäftigte Anforderungsniveau Helfer &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Laufende Raumbeobachtung des BBSR; Beschäftigtenstatistik der Bundesagentur für Arbeit</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t xml:space="preserve">Anteil der SV Beschäftigten am Arbeitsort mit Anforderungsniveau Helfer nach Klassifikation der Berufe 2010 (KldB 2010). Zum Anforderungsniveau Helfer zählen Helfer- und Anlerntätigkeiten mit einfachen, wenig komplexe (Routine-)Tätigkeiten für die entweder eine einjährige (geregelte) Berufsausbildung oder auch kein formaler beruflicher Bildungsabschluss notwendig ist. Die Summe der Anteile ergibt weniger als 100 Prozent, weil die Kategorie 'keine Angabe' nicht in die Berechnung einbezogen ist. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06..
 </t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>3210</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Emp.Helper</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Öffentlich zugängliche Ladepunkte je 100 Elektrofahrzeuge (BEV)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Ladepunkte je 100 Elektrofahrzeuge (BEV)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Öffentliche Ladepunkte &lt;Zeitpunkt&gt; / Elektrofahrzeuge (BEV) &lt;Zeitpunkt&gt; * 100.000</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Laufende Raumbeobachtung des BBSR; Bundesnetzagentur/Ladesäulenverordnung (LSV)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Der Indikator zeigt die Dichte von öffentlich zugänglichen Ladepunkten für Elektrofahrzeuge bezogen auf vorhandene Elektrofahrzeuge an. Eine Ladesäule verfügt in der Regel über mindestens zwei parallel verfügbare Ladepunkte. Es werden hier sowohl Normal- als auch Schnellladepunkte betrachtet. Ländliche Regionen verfügen in der Regel über weniger öffentliche Ladepunkte, da Elektrofahrzeuge hier leichter im privaten Umfeld geladen werden können. Die Zahlen werden von der Bundesnetzagentur im Rahmen der Ladesäulenverordnung (LSV §5) gemeldeten Daten zur öffentlich zugänglichen Ladeinfrastruktur für elektrisch betriebene Fahrzeuge in Deutschland veröffentlicht. Um die Einhaltung der technischen Mindestanforderungen der öffentlich zugänglichen Ladepunkte gemäß der Ladesäulenverordnung (LSV) überprüfen zu können, sind die Betreiberinnen und Betreiber zur Anzeige ihrer öffentlich zugänglichen Ladeinfrastruktur bei der Bundesnetzagentur verpflichtet. Meldepflichtig sind alle öffentlich zugänglichen Ladepunkte mit über 3,7 kW Ladeleistung, die seit dem Inkrafttreten der Verordnung am 17. März 2016 in Betrieb genommen wurden. Schnellladepunkte mit mehr als 22 kW Ladeleistung sind vollständig erfasst. Angaben zu älteren Normalladepunkte und Ladepunkten bis 3,7 kW Ladeleistung basieren auf freiwilligen Meldungen der Betreiber. In den Datenauswertungen sind auch Ladepunkte derjenigen Betreiber öffentlich zugänglicher Ladepunkte enthalten, die einer Veröffentlichung im Ladesäulenregister nicht zugestimmt haben. Ein Ladepunkt ist öffentlich zugänglich, wenn der zum Ladepunkt gehörende Parkplatz von einem unbestimmten oder nur nach allgemeinen Merkmalen bestimmbaren Personenkreis tatsächlich befahren werden kann, es sei denn, der Betreiber hat am Ladepunkt oder in unmittelbarer räumlicher Nähe zum Ladepunkt durch eine deutlich sichtbare Kennzeichnung oder Beschilderung die Nutzung auf einen individuell bestimmten Personenkreis beschränkt. Werte jeweils zum Stichtag 01.01. eines Jahres.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>13209</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Charg.Points.per100EV</t>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anteil von Hybridfahrzeugen am Pkw-Bestand in %</t>
+          <t>Öffentlich zugängliche Ladepunkte je 100 Elektrofahrzeuge (BEV)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pkw Hybrid insgesamt</t>
+          <t>Ladepunkte je 100 Elektrofahrzeuge (BEV)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pkw Hybrid &lt;Zeitpunkt&gt; / Pkw &lt;Zeitpunkt&gt; x 100</t>
+          <t>Öffentliche Ladepunkte &lt;Zeitpunkt&gt; / Elektrofahrzeuge (BEV) &lt;Zeitpunkt&gt; * 100.000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik des Kraftfahrzeugbestandes des Bundes und der Länder</t>
+          <t>Laufende Raumbeobachtung des BBSR; Bundesnetzagentur/Ladesäulenverordnung (LSV)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Der Anteil von Hybridfahrzeugen (also inkl. Plug-In-Hybriden) an allen Personenkraftwagen. Personenkraftwagen die zum Zeitpunkt der Zählung am 01.01. eines jeden Jahres mit einem amtlichen Kennzeichen zum Verkehr zugelassen und im Zentralen Fahrzeugregister des Kraftfahrtbundesamtes gespeichert sind. Personenkraftwagen sind Kraftfahrzeuge zur Personenbeförderung mit mindestens vier Rädern und mit höchstens acht Sitzplätzen außer dem Fahrersitz. Wohnmobile, Krankenwagen, Bestattungswagen und beschussgeschützte Fahrzeuge zählen seit 2005 ebenfalls zu den Personenkraftwagen.</t>
+          <t>Der Indikator zeigt die Dichte von öffentlich zugänglichen Ladepunkten für Elektrofahrzeuge bezogen auf vorhandene Elektrofahrzeuge an. Eine Ladesäule verfügt in der Regel über mindestens zwei parallel verfügbare Ladepunkte. Es werden hier sowohl Normal- als auch Schnellladepunkte betrachtet. Ländliche Regionen verfügen in der Regel über weniger öffentliche Ladepunkte, da Elektrofahrzeuge hier leichter im privaten Umfeld geladen werden können. Die Zahlen werden von der Bundesnetzagentur im Rahmen der Ladesäulenverordnung (LSV §5) gemeldeten Daten zur öffentlich zugänglichen Ladeinfrastruktur für elektrisch betriebene Fahrzeuge in Deutschland veröffentlicht. Um die Einhaltung der technischen Mindestanforderungen der öffentlich zugänglichen Ladepunkte gemäß der Ladesäulenverordnung (LSV) überprüfen zu können, sind die Betreiberinnen und Betreiber zur Anzeige ihrer öffentlich zugänglichen Ladeinfrastruktur bei der Bundesnetzagentur verpflichtet. Meldepflichtig sind alle öffentlich zugänglichen Ladepunkte mit über 3,7 kW Ladeleistung, die seit dem Inkrafttreten der Verordnung am 17. März 2016 in Betrieb genommen wurden. Schnellladepunkte mit mehr als 22 kW Ladeleistung sind vollständig erfasst. Angaben zu älteren Normalladepunkte und Ladepunkten bis 3,7 kW Ladeleistung basieren auf freiwilligen Meldungen der Betreiber. In den Datenauswertungen sind auch Ladepunkte derjenigen Betreiber öffentlich zugänglicher Ladepunkte enthalten, die einer Veröffentlichung im Ladesäulenregister nicht zugestimmt haben. Ein Ladepunkt ist öffentlich zugänglich, wenn der zum Ladepunkt gehörende Parkplatz von einem unbestimmten oder nur nach allgemeinen Merkmalen bestimmbaren Personenkreis tatsächlich befahren werden kann, es sei denn, der Betreiber hat am Ladepunkt oder in unmittelbarer räumlicher Nähe zum Ladepunkt durch eine deutlich sichtbare Kennzeichnung oder Beschilderung die Nutzung auf einen individuell bestimmten Personenkreis beschränkt. Werte jeweils zum Stichtag 01.01. eines Jahres.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Share.Car.Hybrid</t>
+          <t>Charg.Points.per100EV</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anteil Elektrofahrzeuge (BEV) am Pkw-Bestand in %</t>
+          <t>Anteil von Hybridfahrzeugen am Pkw-Bestand in %</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pkw Elektro (BEV)</t>
+          <t>Pkw Hybrid insgesamt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pkw Elektro &lt;Zeitpunkt&gt; / Pkw &lt;Zeitpunkt&gt; x 100</t>
+          <t>Pkw Hybrid &lt;Zeitpunkt&gt; / Pkw &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2047,390 +2272,445 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Der Anteil von reinen Elektrofahrzeugen (also ohne Plug-In-Hybriden) an allen Personenkraftwagen. Personenkraftwagen die zum Zeitpunkt der Zählung am 01.01. eines jeden Jahres mit einem amtlichen Kennzeichen zum Verkehr zugelassen und im Zentralen Fahrzeugregister des Kraftfahrtbundesamtes gespeichert sind. Personenkraftwagen sind Kraftfahrzeuge zur Personenbeförderung mit mindestens vier Rädern und mit höchstens acht Sitzplätzen außer dem Fahrersitz. Wohnmobile, Krankenwagen, Bestattungswagen und beschussgeschützte Fahrzeuge zählen seit 2005 ebenfalls zu den Personenkraftwagen.</t>
+          <t>Der Anteil von Hybridfahrzeugen (also inkl. Plug-In-Hybriden) an allen Personenkraftwagen. Personenkraftwagen die zum Zeitpunkt der Zählung am 01.01. eines jeden Jahres mit einem amtlichen Kennzeichen zum Verkehr zugelassen und im Zentralen Fahrzeugregister des Kraftfahrtbundesamtes gespeichert sind. Personenkraftwagen sind Kraftfahrzeuge zur Personenbeförderung mit mindestens vier Rädern und mit höchstens acht Sitzplätzen außer dem Fahrersitz. Wohnmobile, Krankenwagen, Bestattungswagen und beschussgeschützte Fahrzeuge zählen seit 2005 ebenfalls zu den Personenkraftwagen.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Share.Car.Electro</t>
+          <t>Share.Car.Hybrid</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gesamtangebot an betrieblichen Ausbildungsplätzen je 100 Nachfrager</t>
+          <t>Anteil Elektrofahrzeuge (BEV) am Pkw-Bestand in %</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ausbildungsplätze</t>
+          <t>Pkw Elektro (BEV)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Neu abgeschlossene Ausbildungsverträge und unbesetzte Berufsausbildungsstellen &lt;Zeitpunkt&gt; / Neu abgeschlossene Ausbildungsverträge und noch nicht vermittelte/unversorgte Bewerber &lt;Zeitpunkt&gt; x 100</t>
+          <t>Pkw Elektro &lt;Zeitpunkt&gt; / Pkw &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Berufsbildungsstatistik des Bundesinstituts für Berufsbildung</t>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik des Kraftfahrzeugbestandes des Bundes und der Länder</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bei den 'neu abgeschlossenen Ausbildungsverträgen' handelt es sich um diejenigen Ausbildungsverträge, die in der Zeit vom 01.10. bis 30.09. des folgenden Jahres neu abgeschlossen worden sind und am 30.09. auch noch bestanden haben. 'Unbesetzte Berufsausbildungsstellen' sind alle Ausbildungsstellen, die bis zum Ende des Berichtsjahres weder besetzt noch zurückgenommen worden sind. Als 'noch nicht vermittelte/unversorgte Bewerber' zählen Bewerber, für die bis zum Ende des Berichtsjahres weder die Einmündung in eine Berufsausbildung, noch ein weiterer Schulbesuch, eine Teilnahme an einer Fördermaßnahme oder eine andere Alternative zum 30.09. bekannt ist und für die Vermittlungsbemühungen laufen.</t>
+          <t>Der Anteil von reinen Elektrofahrzeugen (also ohne Plug-In-Hybriden) an allen Personenkraftwagen. Personenkraftwagen die zum Zeitpunkt der Zählung am 01.01. eines jeden Jahres mit einem amtlichen Kennzeichen zum Verkehr zugelassen und im Zentralen Fahrzeugregister des Kraftfahrtbundesamtes gespeichert sind. Personenkraftwagen sind Kraftfahrzeuge zur Personenbeförderung mit mindestens vier Rädern und mit höchstens acht Sitzplätzen außer dem Fahrersitz. Wohnmobile, Krankenwagen, Bestattungswagen und beschussgeschützte Fahrzeuge zählen seit 2005 ebenfalls zu den Personenkraftwagen.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apprent.Positions</t>
+          <t>Share.Car.Electro</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Auszubildende je 1.000 SV Beschäftige</t>
+          <t>Gesamtangebot an betrieblichen Ausbildungsplätzen je 100 Nachfrager</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Auszubildende</t>
+          <t>Ausbildungsplätze</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Auszubildende SV Beschäftigte &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 1.000</t>
+          <t>Neu abgeschlossene Ausbildungsverträge und unbesetzte Berufsausbildungsstellen &lt;Zeitpunkt&gt; / Neu abgeschlossene Ausbildungsverträge und noch nicht vermittelte/unversorgte Bewerber &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
+          <t>Laufende Raumbeobachtung des BBSR; Berufsbildungsstatistik des Bundesinstituts für Berufsbildung</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>In der Beschäftigungsstatistik sind Auszubildende eine Teilmenge der sozialversicherungspflichtig Beschäftigten. Es handelt sich dabei um Personen, die von den Arbeitgebern als Beschäftigte in einem sozialversicherungspflichtigen Ausbildungsverhältnis gemeldet werden. Die Ausbildung kann eine duale Ausbildung in einem staatlich anerkannten Ausbildungsberuf sein. Dazu zählen bspw. auch Studierende in einem dualen Studiengang. Als sozialversicherungspflichtige Auszubildende werden außerdem Beschäftigte in den schulischen Berufsausbildungen gemeldet, in denen ein Ausbildungsentgelt gezahlt wird. Nicht Bestandteil der Auszubildenden in der Beschäftigungsstatistik sind Personen, deren berufliche Ausbildung ausschließlich an beruflichen Schulen ohne sozialversicherungspflichtigen Ausbildungsvertrag, also ohne Sozialversicherungspflicht erfolgt. Es handelt sich um Auszubildende am Arbeitsort.</t>
+          <t>Bei den 'neu abgeschlossenen Ausbildungsverträgen' handelt es sich um diejenigen Ausbildungsverträge, die in der Zeit vom 01.10. bis 30.09. des folgenden Jahres neu abgeschlossen worden sind und am 30.09. auch noch bestanden haben. 'Unbesetzte Berufsausbildungsstellen' sind alle Ausbildungsstellen, die bis zum Ende des Berichtsjahres weder besetzt noch zurückgenommen worden sind. Als 'noch nicht vermittelte/unversorgte Bewerber' zählen Bewerber, für die bis zum Ende des Berichtsjahres weder die Einmündung in eine Berufsausbildung, noch ein weiterer Schulbesuch, eine Teilnahme an einer Fördermaßnahme oder eine andere Alternative zum 30.09. bekannt ist und für die Vermittlungsbemühungen laufen.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Apprent</t>
+          <t>Apprent.Positions</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Anzahl Frauen mit Mandaten in Stadträten und Kreistagen an allen Mandaten in %</t>
+          <t>Auszubildende je 1.000 SV Beschäftige</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(SDG 5) Frauenanteil im Stadtrat bzw. Kreistag</t>
+          <t>Auszubildende</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Anzahl Frauen mit Mandaten in Stadträten und Kreistagen &lt;Zeitpunkt&gt; / Anzahl Mandate in Stadträten und Kreistagen &lt;Zeitpunkt&gt; x 100</t>
+          <t>Auszubildende SV Beschäftigte &lt;Zeitpunkt&gt; / SV Beschäftigte &lt;Zeitpunkt&gt; x 1.000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistische Ämter des Bundes und der Länder - Ergebnisse der Kommunalwahlen, Internetrecherche</t>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Eine höhere Repräsentation von Frauen in öffentlichen Ämtern führt zu einer höheren Berücksichtigung der Interessen von Frauen in den Entscheidungen durch die Mandatsträger. Aus Sicht der intragenerationellen Gerechtigkeit ist eine möglichst paritätische Repräsentation von Frauen und Männern in öffentlichen Mandaten geboten. Der Frauenanteil in Führungspositionen in der Privatwirtschaft, im öffentlichen Dienst und in öffentlichen Ämtern ist trotz massiver Bestrebungen seit Jahren unverändert niedrig. Auf kommunaler Ebene kann ein aktiver Beitrag dazu geleistet werden, damit dieses Missverhältnis abgemildert wird. So können die politischen Parteien über die Zuteilung von Listenplätzen dafür sorgen, dass sich der Frauenanteil in den kommunalen Parlamenten erhöht, damit die Zusammensetzung der Bevölkerung auch in den Stadträten und Kreistagen adäquat abgebildet werden kann. Die Daten werden über eine Internetrecherche aller Stadträte und Kreistage ermittelt. Eine Erhebung erfolgt alle zwei Jahre.</t>
+          <t>In der Beschäftigungsstatistik sind Auszubildende eine Teilmenge der sozialversicherungspflichtig Beschäftigten. Es handelt sich dabei um Personen, die von den Arbeitgebern als Beschäftigte in einem sozialversicherungspflichtigen Ausbildungsverhältnis gemeldet werden. Die Ausbildung kann eine duale Ausbildung in einem staatlich anerkannten Ausbildungsberuf sein. Dazu zählen bspw. auch Studierende in einem dualen Studiengang. Als sozialversicherungspflichtige Auszubildende werden außerdem Beschäftigte in den schulischen Berufsausbildungen gemeldet, in denen ein Ausbildungsentgelt gezahlt wird. Nicht Bestandteil der Auszubildenden in der Beschäftigungsstatistik sind Personen, deren berufliche Ausbildung ausschließlich an beruflichen Schulen ohne sozialversicherungspflichtigen Ausbildungsvertrag, also ohne Sozialversicherungspflicht erfolgt. Es handelt sich um Auszubildende am Arbeitsort.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Share.Women.Council</t>
+          <t>Apprent</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SV beschäftigte Ausländer am Wohnort je 100 erwerbsfähige Ausländer in %</t>
+          <t>Anzahl Frauen mit Mandaten in Stadträten und Kreistagen an allen Mandaten in %</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beschäftigtenquote Ausländer</t>
+          <t>(SDG 5) Frauenanteil im Stadtrat bzw. Kreistag</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SV beschäftigte Ausländer WO &lt;Zeitpunkt&gt; / Ausländer 15 bis &lt; 65 Jahre &lt;Zeitpunkt&gt; x 100</t>
+          <t>Anzahl Frauen mit Mandaten in Stadträten und Kreistagen &lt;Zeitpunkt&gt; / Anzahl Mandate in Stadträten und Kreistagen &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Beschäftigtenstatistik der Bundesagentur für Arbeit</t>
+          <t>Laufende Raumbeobachtung des BBSR; Statistische Ämter des Bundes und der Länder - Ergebnisse der Kommunalwahlen, Internetrecherche</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ausmaß der Erwerbstätigkeit ausländischer Einwohner bezogen auf die Erwerbsfähigen dieser Bevölkerungsgruppe. Es handelt sich um sozialversicherungspflichtig Beschäftigte Ausländer am Wohnort. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei der Bezugsgröße der 15- bis unter 65-Jährigen ist zu beachten, dass sich die Zahlen vor 2011 auf die Fortschreibung auf Basis der Volkszählung 1987 (BRD) und 1981 (DDR) und ab 2011 auf die Fortschreibung auf Basis des Zensus 2011 beziehen. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06., bei der Bevölkerung um Zahlen zum Stichtag 31.12. des Jahres.</t>
+          <t>Eine höhere Repräsentation von Frauen in öffentlichen Ämtern führt zu einer höheren Berücksichtigung der Interessen von Frauen in den Entscheidungen durch die Mandatsträger. Aus Sicht der intragenerationellen Gerechtigkeit ist eine möglichst paritätische Repräsentation von Frauen und Männern in öffentlichen Mandaten geboten. Der Frauenanteil in Führungspositionen in der Privatwirtschaft, im öffentlichen Dienst und in öffentlichen Ämtern ist trotz massiver Bestrebungen seit Jahren unverändert niedrig. Auf kommunaler Ebene kann ein aktiver Beitrag dazu geleistet werden, damit dieses Missverhältnis abgemildert wird. So können die politischen Parteien über die Zuteilung von Listenplätzen dafür sorgen, dass sich der Frauenanteil in den kommunalen Parlamenten erhöht, damit die Zusammensetzung der Bevölkerung auch in den Stadträten und Kreistagen adäquat abgebildet werden kann. Die Daten werden über eine Internetrecherche aller Stadträte und Kreistage ermittelt. Eine Erhebung erfolgt alle zwei Jahre.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Emp.Rate.Foreign</t>
+          <t>Share.Women.Council</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten im Alter von 25 bis unter 55 Jahren in Euro</t>
+          <t>SV beschäftigte Ausländer am Wohnort je 100 erwerbsfähige Ausländer in %</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Medianeinkommen 25 bis unter 55-Jährige</t>
+          <t>Beschäftigtenquote Ausländer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten 25 bis &lt; 55 Jahre in €</t>
+          <t>SV beschäftigte Ausländer WO &lt;Zeitpunkt&gt; / Ausländer 15 bis &lt; 65 Jahre &lt;Zeitpunkt&gt; x 100</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
+          <t>Laufende Raumbeobachtung des BBSR; Beschäftigtenstatistik der Bundesagentur für Arbeit</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Median der monatlichen Bruttoarbeitsentgelte von sozialversicherungspflichtig Vollzeitbeschäftigten am Arbeitsort im Alter von 25 bis unter 55 Jahren. Der Median (auch Zentralwert) gibt den mittleren Wert einer der Göße nach sortierten Verteilung von Messwerten an und teilt damit den Datensatz in zwei gleich große Hälften. Somit ist er im Vergleich zum arithmetischen Mittel robuster gegenüber Ausreißern. Der geschlechtsdifferenzierte Indikator deutet an, dass die Ausprägung für die Gruppe der Männer (deutlich) von der Gesamtsituation abweichen kann. Vergleiche zu den Vorjahren sind nicht oder nur eingeschränkt  möglich wegen eines 2011 eingeführten neuen Verfahrens, mit dem die Arbeitgeber ihre Meldungen über Voll- und Teilzeitbeschäftigung an die BA weitergeben. Die Informationen über die Inhalte des neuen Erhebungsverfahrens lagen nicht gleichzeitig zu einem bestimmten Stichtag vor, stattdessen gab es eine zweijährige Übergangsphase.</t>
+          <t>Ausmaß der Erwerbstätigkeit ausländischer Einwohner bezogen auf die Erwerbsfähigen dieser Bevölkerungsgruppe. Es handelt sich um sozialversicherungspflichtig Beschäftigte Ausländer am Wohnort. Sozialversicherungspflichtig Beschäftigte sind Arbeiter, Angestellte und Personen in beruflicher Ausbildung, die in der gesetzlicher Renten-, Kranken- und/oder Arbeitslosenversicherung pflichtversichert sind. Keine Berücksichtigung finden hier also Beamte, Selbständige, mithelfende Familienangehörige oder geringfügig Beschäftigte. Insgesamt werden so nur rund 75% aller Erwerbstätigen erfasst. Trotz dieser Einschränkung werden die sozialversicherungspflichtig Beschäftigten als Maß der dem Arbeitsmarkt zur Verfügung stehenden Arbeitsplätze verwendet. Bei der Bezugsgröße der 15- bis unter 65-Jährigen ist zu beachten, dass sich die Zahlen vor 2011 auf die Fortschreibung auf Basis der Volkszählung 1987 (BRD) und 1981 (DDR) und ab 2011 auf die Fortschreibung auf Basis des Zensus 2011 beziehen. Bei den Beschäftigten handelt es sich um Zahlen zum Stichtag 30.06., bei der Bevölkerung um Zahlen zum Stichtag 31.12. des Jahres.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Income.Median.Age25to54</t>
+          <t>Emp.Rate.Foreign</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten im Alter von 25 bis unter 55 Jahren in Euro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Medianeinkommen 25 bis unter 55-Jährige</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten 25 bis &lt; 55 Jahre in €</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Median der monatlichen Bruttoarbeitsentgelte von sozialversicherungspflichtig Vollzeitbeschäftigten am Arbeitsort im Alter von 25 bis unter 55 Jahren. Der Median (auch Zentralwert) gibt den mittleren Wert einer der Göße nach sortierten Verteilung von Messwerten an und teilt damit den Datensatz in zwei gleich große Hälften. Somit ist er im Vergleich zum arithmetischen Mittel robuster gegenüber Ausreißern. Der geschlechtsdifferenzierte Indikator deutet an, dass die Ausprägung für die Gruppe der Männer (deutlich) von der Gesamtsituation abweichen kann. Vergleiche zu den Vorjahren sind nicht oder nur eingeschränkt  möglich wegen eines 2011 eingeführten neuen Verfahrens, mit dem die Arbeitgeber ihre Meldungen über Voll- und Teilzeitbeschäftigung an die BA weitergeben. Die Informationen über die Inhalte des neuen Erhebungsverfahrens lagen nicht gleichzeitig zu einem bestimmten Stichtag vor, stattdessen gab es eine zweijährige Übergangsphase.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>6006</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Income.Median.Age25to54</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten im Alter von 55 bis unter 65 Jahren in Euro</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Medianeinkommen 55 bis unter 65-Jährige</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Medianeinkommen der sozialversicherungspflichtig Vollzeitbeschäftigten 55 bis &lt; 65 Jahre in €</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">Median der monatlichen Bruttoarbeitsentgelte von sozialversicherungspflichtig Vollzeitbeschäftigten (der Kerngruppe) am Arbeitsort. Der Median (auch Zentralwert) gibt den mittleren Wert einer der Göße nach sortierten Verteilung von Messwerten an und teilt damit den Datensatz in zwei gleich große Hälften. Somit ist er im Vergleich zum arithmetischen Mittel robuster gegenüber Ausreißern. Vergleiche zu den Vorjahren sind nicht oder nur eingeschränkt  möglich wegen eines 2011 eingeführten neuen Verfahrens, mit dem die Arbeitgeber ihre Meldungen über Voll- und Teilzeitbeschäftigung an die BA weitergeben. Die Informationen über die Inhalte des neuen Erhebungsverfahrens lagen nicht gleichzeitig zu einem bestimmten Stichtag vor, stattdessen gab es eine zweijährige Übergangsphase.
 Die Berechnung der Werte für die Raumeinheiten (nicht Kreiswerte) sind mit Hilfe der Kreiswerte geschätzt. 
 </t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>6007</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Income.Median.Age55to64</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Medianeinkommen der vollzeitbeschäftigten Frauen im Verhältnis zu dem Medianeinkommen der vollzeitbeschäftigten Männer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Verdienstabstand zwischen Frauen und Männern</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bruttomonatsentgeld einer weiblichen Vollzeitbeschäftigten &lt;Zeitpunkt&gt; / Bruttomonatsentgeld eines männlichen Vollzeitbeschäftigten &lt;Zeitpunkt&gt; x 100</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Noch immer existieren signifikante Einkommensunterschiede zwischen weiblichen und männlichen Arbeitnehmern. Diese Unterschiede sind z.T. auf die Wahl unterschiedlicher Berufe, den Aufstieg in den unterschiedlich vergüteten Hierarchiegruppen, der Berücksictigung von Berufserfahrung - ein familienbedingter, befristeter Ausstieg wirkt sich negativ auf die Einkommen aus - zurückzuführen. Zum anderen werden Frauen trotz Diskriminierungsverbots für gleichwertige Arbeit niedriger entlohnt. Bei der Betrachtung des Medianeinkommens werden lediglich Informationen vollzeitbeschäftigter Frauen und Männer herangezogen, informelle und Teilzeitbeschäftigungsverhältnisse werden nicht berücksichtigt. Dies ist vor allem dann problematisch, wenn systematische Unterschiede zwischen Frauen und Männern auf dem Arbeitsmarkt bestehen.</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>6010</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Pay.Gap.Gender</t>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Medianeinkommen der vollzeitbeschäftigten Frauen im Verhältnis zu dem Medianeinkommen der vollzeitbeschäftigten Männer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Verdienstabstand zwischen Frauen und Männern</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bruttomonatsentgeld einer weiblichen Vollzeitbeschäftigten &lt;Zeitpunkt&gt; / Bruttomonatsentgeld eines männlichen Vollzeitbeschäftigten &lt;Zeitpunkt&gt; x 100</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik der Bundesagentur für Arbeit</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Noch immer existieren signifikante Einkommensunterschiede zwischen weiblichen und männlichen Arbeitnehmern. Diese Unterschiede sind z.T. auf die Wahl unterschiedlicher Berufe, den Aufstieg in den unterschiedlich vergüteten Hierarchiegruppen, der Berücksictigung von Berufserfahrung - ein familienbedingter, befristeter Ausstieg wirkt sich negativ auf die Einkommen aus - zurückzuführen. Zum anderen werden Frauen trotz Diskriminierungsverbots für gleichwertige Arbeit niedriger entlohnt. Bei der Betrachtung des Medianeinkommens werden lediglich Informationen vollzeitbeschäftigter Frauen und Männer herangezogen, informelle und Teilzeitbeschäftigungsverhältnisse werden nicht berücksichtigt. Dies ist vor allem dann problematisch, wenn systematische Unterschiede zwischen Frauen und Männern auf dem Arbeitsmarkt bestehen.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6010</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pay.Gap.Gender</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Bruttoinlandsprodukt in 1.000 € je Einwohner</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Bruttoinlandsprodukt je Einwohner</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Bruttoinlandsprodukt &lt;Zeitpunkt&gt; / E &lt;Zeitpunkt&gt; / 1.000</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Laufende Raumbeobachtung des BBSR; Volkswirtschaftliche Gesamtrechnung der Länder</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">Bei Bezug auf die Bevölkerung als Wohlstandsmaß zu interpretieren. Das BIP bzw. die BWS ist ein Maß für die ein einer Region erbrachte wirtschaftliche Leistung. Die BWS je Wirtschaftsbereich wird berechnet, indem vom Wert aller produzierten Waren und Dienstleistungen die bei der Produktion verbrauchten Vorleistungen (Roh-, Hilfs- und Betriebsstoffe, Mieten und Pachten, Kosten für durch andere Unternehmen durchgeführte Lohnarbeiten etc.) abgezogen werden. Die Bewertung der BWS erfolgt zu Herstellungspreisen. Dieses Bewertungskonzept bedeutet, dass die auf die produzierten oder verkauften Waren und Dienstleistungen gewährten Gütersubventionen einbezogen sind, nicht aber die auf die produzierten Waren und Dienstleistungen zu zahlenden Gütersteuern (Mehrwertsteuer, Importabgaben, Mineralöl- und Tabaksteuer etc.). Das BIP wird zu Marktpreisen bewertet. Es wird berechnet, indem zur gesamten BWS zu Herstellungspreisen der auf die Kreise pauschal verteilte Saldo aus Gütersteuern – Gütersubventionen hinzu addiert wird. Die Finanzserviceleistung indirekte Messung (FISIM) ist implizit in den Wirtschaftsbereichen bereits berücksichtigt. Bei den Bevölkerungszahlen handelt es sich um die Fortschreibung des Bevölkerungsstandes des Bundes und der Länder zum Stichtag 31.12. des Jahres. Die Fortschreibung basiert auf der Volkszählung 1987 (BRD) bzw. 1981 (DDR), dem Zensus 2011 sowie dem Zensus 2022.
 </t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>14205</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>GDP.perCapita</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Durchschnittliche Kaufwerte für Bauland in € je m²</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Baulandpreise</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Kaufsumme für baureifes Land &lt;Durchschnitt zwei Jahre&gt; / Umgesetzte Fläche für baureifes Land &lt;Durchschnitt zwei Jahre&gt;</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Laufende Raumbeobachtung des BBSR; Statistik der Kaufwerte für Bauland des Bundes und der Länder</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Grundstückspreise können je nach Marktlage einen hohen Anteil an den Bau- und Immobilienkosten ausmachen. Die Kaufsumme ist die Gesamtsumme aus den Kaufpreisen der veräußerten Grundstücke. Der Kaufpreis für das Grundstück versteht sich ohne Grunderwerbsnebenkosten (Vermessungskosten, Makler-, Notariats- und Gerichtsgebühren, Grunderwerbsteuer u.a.). Er beinhaltet jedoch evtl. besonders vereinbarte Beträge für Aufwuchs, Zäune, den Kapitalwert von Leibrenten sowie die Erschließungskosten. Die veräußerte Fläche umschließt alle durch Kauf erworbenen, unbebauten Grundstücke innerhalb des Baugebiets einer Gemeinde einer Mindestgröße von 100 m². Der Zwei-Jahresdurchschnitt federt kurzfristige Schwankungen auf dem Markt und in der Statistik ab, die durch Veröffentlichungsrestriktionen und Art der Veräußerungsfälle entstehen können.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Land.Price</t>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hausärzte je 10.000 Einwohner</t>
+          <t>Durchschnittliche Kaufwerte für Bauland in € je m²</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hausärzte</t>
+          <t>Baulandpreise</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hausärzte &lt;Zeitpunkt&gt; / E &lt;Zeitpunkt&gt; x 10.000</t>
+          <t>Kaufsumme für baureifes Land &lt;Durchschnitt zwei Jahre&gt; / Umgesetzte Fläche für baureifes Land &lt;Durchschnitt zwei Jahre&gt;</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Laufende Raumbeobachtung des BBSR; Kassenärztliche Bundesvereinigung</t>
+          <t>Laufende Raumbeobachtung des BBSR; Statistik der Kaufwerte für Bauland des Bundes und der Länder</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hausärzte ohne Kinderärzte, inkl. Angestellte. Die Basiszahlen, aus denen die Indikatoren zur ärztlichen Versorgung berechnet wurden, enthalten Missing-Werte (Geheimhaltungsfälle). Diese wurden durch geschätzte Werte ersetzt, was zu voneinander abweichenden Indikatorenwerten der räumlichen Aggregate in den Themenbereichen 'Medizinische Versorgung' (Basis: Kreise) und 'Zentrale Orte Monitoring/Gesundheitsversorgungsfunktion' (Basis: Gemeinden) führt. Die Indikatorenwerte dienen nur zum Vergleich von Größenordnungen, sie sind nicht verbindlich. </t>
+          <t>Grundstückspreise können je nach Marktlage einen hohen Anteil an den Bau- und Immobilienkosten ausmachen. Die Kaufsumme ist die Gesamtsumme aus den Kaufpreisen der veräußerten Grundstücke. Der Kaufpreis für das Grundstück versteht sich ohne Grunderwerbsnebenkosten (Vermessungskosten, Makler-, Notariats- und Gerichtsgebühren, Grunderwerbsteuer u.a.). Er beinhaltet jedoch evtl. besonders vereinbarte Beträge für Aufwuchs, Zäune, den Kapitalwert von Leibrenten sowie die Erschließungskosten. Die veräußerte Fläche umschließt alle durch Kauf erworbenen, unbebauten Grundstücke innerhalb des Baugebiets einer Gemeinde einer Mindestgröße von 100 m². Der Zwei-Jahresdurchschnitt federt kurzfristige Schwankungen auf dem Markt und in der Statistik ab, die durch Veröffentlichungsrestriktionen und Art der Veräußerungsfälle entstehen können.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Physician.GP</t>
+          <t>Land.Price</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>
@@ -2471,6 +2751,11 @@
           <t>Vote.Share.UNION</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2509,6 +2794,11 @@
           <t>Vote.Share.SPD</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2547,6 +2837,11 @@
           <t>Vote.Share.Gruene</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2585,6 +2880,11 @@
           <t>Vote.Share.FDP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2623,6 +2923,11 @@
           <t>Vote.Share.Other</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2661,6 +2966,11 @@
           <t>Vote.Share.LINKE</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>INKAR</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2697,6 +3007,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>Vote.Share.AFD</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>INKAR</t>
         </is>
       </c>
     </row>

--- a/Work/Data_Info/Meta_kre.xlsx
+++ b/Work/Data_Info/Meta_kre.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>New.Housing.per.Capita</t>
+          <t>New_Housing_per_Capita</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Permit.Housing.perCapita</t>
+          <t>Permit_Housing_perCapita</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Age.below.6</t>
+          <t>Age_below_6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Age.6.18</t>
+          <t>Age_6_18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Age.65</t>
+          <t>Age_65</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>School.Primary</t>
+          <t>School_Primary</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>School.SpecialEdu</t>
+          <t>School_SpecialEdu</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Migration.Balance</t>
+          <t>Migration_Balance</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Purchasing.Power</t>
+          <t>Purchasing_Power</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Recreation.Area.per.Capita</t>
+          <t>Recreation_Area_per_Capita</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Forest.Area</t>
+          <t>Forest_Area</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Water.Area</t>
+          <t>Water_Area</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Population.Density</t>
+          <t>Population_Density</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Highway.Access</t>
+          <t>Highway_Access</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Airport.Access</t>
+          <t>Airport_Access</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Highspeed.Rail.Access</t>
+          <t>Highspeed_Rail_Access</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Supermarket.Access</t>
+          <t>Supermarket_Access</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Doc.GP</t>
+          <t>Doc_GP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pharmacy.Access</t>
+          <t>Pharmacy_Access</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Broadband.50Mbps</t>
+          <t>Broadband_50Mbps</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Broadband.100Mbps</t>
+          <t>Broadband_100Mbps</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Broadband.1000Mbps</t>
+          <t>Broadband_1000Mbps</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Public.Transport.Access</t>
+          <t>Public_Transport_Access</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Traffic.Accidents</t>
+          <t>Traffic_Accidents</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Child.Poverty</t>
+          <t>Child_Poverty</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emp.Rate</t>
+          <t>Emp_Rate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Emp.Rate.Women</t>
+          <t>Emp_Rate_Women</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unemp.Men</t>
+          <t>Unemp_Men</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Investment.Allocations</t>
+          <t>Investment_Allocations</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Land.Price</t>
+          <t>Land_Price</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Emp.Primary</t>
+          <t>Emp_Primary</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Emp.Secundary</t>
+          <t>Emp_Secundary</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emp.Tertiary</t>
+          <t>Emp_Tertiary</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Emp.Creative</t>
+          <t>Emp_Creative</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Emp.AO.Academic</t>
+          <t>Emp_AO_Academic</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Emp.AO.Vocational</t>
+          <t>Emp_AO_Vocational</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emp.AO.NoTrain</t>
+          <t>Emp_AO_NoTrain</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emp.Expert</t>
+          <t>Emp_Expert</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Emp.Specialist</t>
+          <t>Emp_Specialist</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Emp.Professional</t>
+          <t>Emp_Professional</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Emp.Helper</t>
+          <t>Emp_Helper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Charg.Points.per100EV</t>
+          <t>Charg_Points_per100EV</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Share.Car.Hybrid</t>
+          <t>Share_Car_Hybrid</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Share.Car.Electro</t>
+          <t>Share_Car_Electro</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Apprent.Positions</t>
+          <t>Apprent_Positions</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Share.Women.Council</t>
+          <t>Share_Women_Council</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Emp.Rate.Foreign</t>
+          <t>Emp_Rate_Foreign</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Income.Median.Age25to54</t>
+          <t>Income_Median_Age25to54</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Income.Median.Age55to64</t>
+          <t>Income_Median_Age55to64</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pay.Gap.Gender</t>
+          <t>Pay_Gap_Gender</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GDP.perCapita</t>
+          <t>GDP_perCapita</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Land.Price</t>
+          <t>Land_Price</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Vote.Share.UNION</t>
+          <t>Vote_Share_UNION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Vote.Share.SPD</t>
+          <t>Vote_Share_SPD</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Vote.Share.Gruene</t>
+          <t>Vote_Share_Gruene</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Vote.Share.FDP</t>
+          <t>Vote_Share_FDP</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Vote.Share.Other</t>
+          <t>Vote_Share_Other</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Vote.Share.LINKE</t>
+          <t>Vote_Share_LINKE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Vote.Share.AFD</t>
+          <t>Vote_Share_AFD</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
